--- a/comparacao_matriculas/matriculas_na_captacao_que_nao_estao_na_planilha.xlsx
+++ b/comparacao_matriculas/matriculas_na_captacao_que_nao_estao_na_planilha.xlsx
@@ -1,40 +1,279 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="76">
+  <si>
+    <t>Situação Inscrição</t>
+  </si>
+  <si>
+    <t>Numero Inscricao</t>
+  </si>
+  <si>
+    <t>Nome Completo</t>
+  </si>
+  <si>
+    <t>Situação de Avaliação</t>
+  </si>
+  <si>
+    <t>Curso ID</t>
+  </si>
+  <si>
+    <t>Unidade Inscrito</t>
+  </si>
+  <si>
+    <t>Forma de Ingresso</t>
+  </si>
+  <si>
+    <t>createdon</t>
+  </si>
+  <si>
+    <t>cad_inscricaocandidatoid</t>
+  </si>
+  <si>
+    <t>Data Aprovação</t>
+  </si>
+  <si>
+    <t>Data de Pagamento</t>
+  </si>
+  <si>
+    <t>Situação Pagamento</t>
+  </si>
+  <si>
+    <t>Matriculado</t>
+  </si>
+  <si>
+    <t>CAN-005526-TRI</t>
+  </si>
+  <si>
+    <t>CAN-005477-TRI</t>
+  </si>
+  <si>
+    <t>CAN-005476-TRI</t>
+  </si>
+  <si>
+    <t>CAN-005271-TRI</t>
+  </si>
+  <si>
+    <t>CAN-004644-TRI</t>
+  </si>
+  <si>
+    <t>CAN-004619-TRI</t>
+  </si>
+  <si>
+    <t>CAN-004416-TRI</t>
+  </si>
+  <si>
+    <t>CAN-001252-TRI</t>
+  </si>
+  <si>
+    <t>Virginha de Nazaré Oliveira Ferreira</t>
+  </si>
+  <si>
+    <t>Vitória Maria Brito</t>
+  </si>
+  <si>
+    <t>Ana Carolina Domingues</t>
+  </si>
+  <si>
+    <t>Luciani Aparecida Lemes França Velloso</t>
+  </si>
+  <si>
+    <t>Luiz Felipe Soares</t>
+  </si>
+  <si>
+    <t>Daniela Christina Toledo Werneck de Rezende</t>
+  </si>
+  <si>
+    <t>Emmanuel Lamins Moreira Silva</t>
+  </si>
+  <si>
+    <t>Paulo Victor Pereira Silva</t>
+  </si>
+  <si>
+    <t>Apto para Avaliação</t>
+  </si>
+  <si>
+    <t>Avaliado</t>
+  </si>
+  <si>
+    <t>Biomedicina</t>
+  </si>
+  <si>
+    <t>Farmácia</t>
+  </si>
+  <si>
+    <t>Terapia Ocupacional</t>
+  </si>
+  <si>
+    <t>Nutrição</t>
+  </si>
+  <si>
+    <t>Ansiedade e Depressão: Intervenções em Terapia Cognitivo-Comportamental</t>
+  </si>
+  <si>
+    <t>Primeiros Socorros na Prática para Profissionais da Saúde</t>
+  </si>
+  <si>
+    <t>Administração</t>
+  </si>
+  <si>
+    <t>Transferencia - Faculdade Serra Dourada Altamira</t>
+  </si>
+  <si>
+    <t>Retorno - Faculdade Serra Dourada Altamira</t>
+  </si>
+  <si>
+    <t>Histórico Ensino Médio - Faculdade Serra Dourada Lorena</t>
+  </si>
+  <si>
+    <t>Histórico Ensino Médio - Faculdade Serra Dourada Altamira</t>
+  </si>
+  <si>
+    <t>Cursos Livres - Faculdade Serra Dourada Lorena</t>
+  </si>
+  <si>
+    <t>PAGAMENTO / INTEGRAÇÃO TOTVS</t>
+  </si>
+  <si>
+    <t>2026-08-14T11:29:54-03:00</t>
+  </si>
+  <si>
+    <t>2026-08-13T18:20:44-03:00</t>
+  </si>
+  <si>
+    <t>2026-08-13T18:07:39-03:00</t>
+  </si>
+  <si>
+    <t>2026-08-11T10:06:29-03:00</t>
+  </si>
+  <si>
+    <t>2026-07-30T09:29:03-03:00</t>
+  </si>
+  <si>
+    <t>2026-07-29T17:53:21-03:00</t>
+  </si>
+  <si>
+    <t>2026-07-24T19:18:24-03:00</t>
+  </si>
+  <si>
+    <t>2026-05-12T17:48:54-03:00</t>
+  </si>
+  <si>
+    <t>{89206E9D-EC97-F111-B8DC-00224836B90D}</t>
+  </si>
+  <si>
+    <t>{D24E4ED6-5C97-F111-B8DC-7CED8DB11FB7}</t>
+  </si>
+  <si>
+    <t>{A3AEAB02-5B97-F111-B8DC-000D3AC0F764}</t>
+  </si>
+  <si>
+    <t>{149FAC73-8595-F111-B8DC-000D3AC0F764}</t>
+  </si>
+  <si>
+    <t>{D500D13C-128C-F111-8077-00224836BDFB}</t>
+  </si>
+  <si>
+    <t>{2FF76983-8F8B-F111-8077-7CED8DB11FB7}</t>
+  </si>
+  <si>
+    <t>{37048995-AD87-F111-AB0F-70A8A5A98587}</t>
+  </si>
+  <si>
+    <t>{D77E45F9-434E-F111-BEC7-7CED8DA8AD31}</t>
+  </si>
+  <si>
+    <t>2026-08-14T11:32:16-03:00</t>
+  </si>
+  <si>
+    <t>2026-08-13T18:23:10-03:00</t>
+  </si>
+  <si>
+    <t>2026-08-13T18:09:34-03:00</t>
+  </si>
+  <si>
+    <t>2026-08-11T10:07:37-03:00</t>
+  </si>
+  <si>
+    <t>2026-07-30T09:30:10-03:00</t>
+  </si>
+  <si>
+    <t>2026-07-29T17:54:37-03:00</t>
+  </si>
+  <si>
+    <t>2026-07-24T19:19:27-03:00</t>
+  </si>
+  <si>
+    <t>2026-05-12T17:49:40-03:00</t>
+  </si>
+  <si>
+    <t>2026-08-14T03:00:00-03:00</t>
+  </si>
+  <si>
+    <t>2026-08-13T03:00:00-03:00</t>
+  </si>
+  <si>
+    <t>2026-08-11T03:00:00-03:00</t>
+  </si>
+  <si>
+    <t>2026-07-30T00:00:00-03:00</t>
+  </si>
+  <si>
+    <t>2026-07-29T18:03:34-03:00</t>
+  </si>
+  <si>
+    <t>2026-07-24T19:38:20-03:00</t>
+  </si>
+  <si>
+    <t>2026-05-12T14:53:24-03:00</t>
+  </si>
+  <si>
+    <t>Pago</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +281,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,62 +598,329 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nome Completo_x</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>cpf</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ID Lead</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Proprietário</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Situação Inscrição</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Número Inscrição</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Unidade Lead</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Unidade Form</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Oferta Atual</t>
-        </is>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" t="s">
+        <v>63</v>
+      </c>
+      <c r="K5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>71</v>
+      </c>
+      <c r="L6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" t="s">
+        <v>73</v>
+      </c>
+      <c r="L8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L9" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>